--- a/data/User.xlsx
+++ b/data/User.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0B0DFC-D737-4F53-BD80-E6E9679AEE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5054F1CE-B857-4431-B830-00CCCD67EECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="141">
   <si>
     <t>id</t>
   </si>
@@ -54,16 +43,6 @@
   </si>
   <si>
     <t>最後更新日期</t>
-  </si>
-  <si>
-    <t>2025-10-03 15:09:42</t>
-  </si>
-  <si>
-    <t>2025-10-07 14:18:26</t>
-  </si>
-  <si>
-    <t>2025-10-07 14:18:26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>主鍵 id</t>
@@ -98,13 +77,6 @@
     <t>James</t>
   </si>
   <si>
-    <t>2025-10-21 13:59:20</t>
-  </si>
-  <si>
-    <t>2025-10-21 13:59:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
@@ -369,19 +341,132 @@
     <t>zoe@test.com</t>
   </si>
   <si>
-    <t>2025-11-01 17:53:46</t>
-  </si>
-  <si>
-    <t>2025-11-01 17:53:46</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>meri@test.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Meri</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-03-18 14:22:51</t>
+  </si>
+  <si>
+    <t>2024-07-02 09:11:37</t>
+  </si>
+  <si>
+    <t>2024-11-25 18:45:03</t>
+  </si>
+  <si>
+    <t>2024-01-09 06:33:28</t>
+  </si>
+  <si>
+    <t>2024-09-14 21:17:42</t>
+  </si>
+  <si>
+    <t>2024-05-30 12:58:16</t>
+  </si>
+  <si>
+    <t>2024-02-21 03:49:55</t>
+  </si>
+  <si>
+    <t>2024-12-04 16:27:39</t>
+  </si>
+  <si>
+    <t>2024-06-10 10:05:44</t>
+  </si>
+  <si>
+    <t>2024-08-19 23:41:07</t>
+  </si>
+  <si>
+    <t>2024-04-07 19:26:18</t>
+  </si>
+  <si>
+    <t>2024-10-12 08:14:59</t>
+  </si>
+  <si>
+    <t>2024-01-27 15:36:22</t>
+  </si>
+  <si>
+    <t>2024-03-03 11:02:47</t>
+  </si>
+  <si>
+    <t>2024-11-08 20:55:31</t>
+  </si>
+  <si>
+    <t>2024-07-21 04:18:09</t>
+  </si>
+  <si>
+    <t>2024-09-01 13:47:52</t>
+  </si>
+  <si>
+    <t>2024-05-16 17:39:40</t>
+  </si>
+  <si>
+    <t>2024-12-29 22:08:33</t>
+  </si>
+  <si>
+    <t>2024-02-14 07:25:11</t>
+  </si>
+  <si>
+    <t>2024-06-28 01:54:26</t>
+  </si>
+  <si>
+    <t>2024-10-05 14:33:19</t>
+  </si>
+  <si>
+    <t>2024-04-19 09:42:57</t>
+  </si>
+  <si>
+    <t>2024-08-07 18:21:35</t>
+  </si>
+  <si>
+    <t>2024-03-30 05:16:48</t>
+  </si>
+  <si>
+    <t>2024-11-17 12:03:14</t>
+  </si>
+  <si>
+    <t>2024-01-15 20:29:56</t>
+  </si>
+  <si>
+    <t>2024-07-09 16:44:02</t>
+  </si>
+  <si>
+    <t>2024-09-23 02:37:25</t>
+  </si>
+  <si>
+    <t>2024-05-03 11:59:41</t>
+  </si>
+  <si>
+    <t>2024-12-11 19:07:53</t>
+  </si>
+  <si>
+    <t>2024-02-05 08:48:12</t>
+  </si>
+  <si>
+    <t>2024-06-03 15:22:36</t>
+  </si>
+  <si>
+    <t>2024-10-27 21:13:05</t>
+  </si>
+  <si>
+    <t>2024-04-25 10:34:49</t>
+  </si>
+  <si>
+    <t>2024-08-30 06:57:18</t>
+  </si>
+  <si>
+    <t>2024-03-11 23:15:27</t>
+  </si>
+  <si>
+    <t>2024-11-02 17:28:44</t>
+  </si>
+  <si>
+    <t>2024-01-04 13:09:38</t>
+  </si>
+  <si>
+    <t>2025-01-03 22:41:50</t>
   </si>
 </sst>
 </file>
@@ -803,22 +888,22 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>13</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>16</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>3</v>
@@ -835,19 +920,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>15</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>1</v>
@@ -864,25 +949,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -895,25 +980,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -927,25 +1012,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -959,25 +1044,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -991,25 +1076,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -1020,25 +1105,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -1052,25 +1137,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -1084,25 +1169,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1116,25 +1201,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -1148,25 +1233,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1180,25 +1265,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1212,25 +1297,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -1244,25 +1329,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -1276,25 +1361,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -1308,25 +1393,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -1340,25 +1425,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -1372,25 +1457,25 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -1404,25 +1489,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -1436,25 +1521,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -1468,25 +1553,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -1500,25 +1585,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -1532,25 +1617,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -1564,25 +1649,25 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -1596,25 +1681,25 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -1628,25 +1713,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -1660,25 +1745,25 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -1692,25 +1777,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -1724,25 +1809,25 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -1756,25 +1841,25 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -1788,25 +1873,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -1820,25 +1905,25 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
@@ -1852,25 +1937,25 @@
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -1884,25 +1969,25 @@
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -1916,25 +2001,25 @@
         <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -1948,25 +2033,25 @@
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -1980,25 +2065,25 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -2012,25 +2097,25 @@
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -2044,25 +2129,25 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
@@ -2076,25 +2161,25 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
@@ -2108,25 +2193,25 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
